--- a/SmartHospitalTesting/src/test/resources/test_datas/Tamilarasu_data/Search_item_data.xlsx
+++ b/SmartHospitalTesting/src/test/resources/test_datas/Tamilarasu_data/Search_item_data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{89FF6C83-09FA-4D51-BD4D-633D05A9CA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{415A1093-44C3-46E9-9686-8559CB5F6ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:N7"/>
+  <oleSize ref="A1:K5"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,12 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t xml:space="preserve">search_By_name </t>
-  </si>
-  <si>
-    <t>Syringe</t>
   </si>
   <si>
     <t>Bed Sheet</t>
@@ -421,22 +418,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -454,17 +451,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -483,30 +480,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C2">
         <v>123456756</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -527,27 +524,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>123456756</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
